--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_06_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_06_18_Cau.xlsx
@@ -678,7 +678,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xét lúc source trễ, task giữa DAG fail và cần chạy lại một date range.</t>
+          <t>Để vận hành một pipeline dữ liệu tin cậy trong môi trường sản xuất, ngoài lịch chạy cron cần bổ sung các yêu cầu bắt buộc: (a) Đồ thị phụ thuộc dữ liệu và điều kiện sẵn sàng của dữ liệu nguồn (dependency graph / data sensors); (b) Chính sách thử lại riêng cho từng tác vụ kèm giới hạn tối đa; (c) Cơ chế cảnh báo vi phạm SLA, người sở hữu phụ trách và khả năng hiển thị trạng thái thực thi; (d) Các tham số chạy bù dữ liệu có chặn giới hạn (bounded backfill) và quản lý dấu vết dữ liệu (lineage).</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không write trực tiếp vào alias đang serve.</t>
+          <t>Quy trình phát hành chỉ mục vector nguyên tử (atomic vector index publish) bảo đảm tính sẵn sàng: 1. Xây dựng bộ sưu tập staging độc lập (build staging collection) (o2) -&gt; 2. Xác minh số lượng bản ghi, schema, mẫu dữ liệu và manifest trên staging (o1) -&gt; 3. Chuyển đổi alias phục vụ sang bộ sưu tập staging một cách nguyên tử (switch serving alias atomically) (o3) -&gt; 4. Duy trì snapshot phiên bản phục vụ trước đó trong khoảng thời gian an toàn (o4) -&gt; 5. Rollback alias về snapshot cũ nếu các phép kiểm sau phát hành thất bại (o5).</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định incident trước, rồi dùng signal rộng/rẻ trước targeted lineage.</t>
+          <t>Trình tự phân loại và xử lý sự cố dữ liệu (data incident triage) tối ưu chi phí và thời gian: 1. Ghi nhận triệu chứng sự cố, vi phạm SLA, phạm vi ảnh hưởng và giả thuyết ban đầu (o5) -&gt; 2. Kiểm tra độ tươi mới và mốc chạy thành công gần nhất (freshness/last success) (o2) -&gt; 3. Kiểm tra khối lượng dữ liệu và tỷ lệ lỗi theo từng giai đoạn đường ống (volume/stage errors) (o4) -&gt; 4. Kiểm tra các thay đổi về cấu trúc schema hoặc hợp đồng dữ liệu gần đây (o1) -&gt; 5. Truy vết ngược dòng lineage chi tiết về tận nguồn dữ liệu và người sở hữu phụ trách (o3).</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Verify từ source tới bề mặt agent.</t>
+          <t>Bằng chứng kỹ thuật đầy đủ và thuyết phục để chính thức đóng một sự cố dữ liệu (data incident) bao gồm: (a) Bản ghi nguồn và bản ghi chuẩn hóa đã được xác minh đúng kèm đầy đủ lineage; (b) Các tín hiệu kiểm tra chất lượng dữ liệu liên quan đã vượt qua thành công; (c) Snapshot đang hoạt động ở tầng phục vụ mang đúng ID phiên bản đã khắc phục; (d) Truy vấn thực tế của người dùng ban đầu được chạy lại và trả về câu trả lời cùng trích dẫn nguồn hoàn toàn chính xác.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_06_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_06_18_Cau.xlsx
@@ -624,10 +624,24 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Liệt kê hành vi khi source chưa sẵn sàng và task giữa DAG fail.
-Phân tích theo nguyên lý thiết kế: Liệt kê hành vi khi source chưa sẵn sàng và task giữa DAG fail.</t>
+- [1.5 điểm] Xây dựng đầy đủ bảng yêu cầu kỹ thuật cho Orchestrator đáp ứng đủ: sensor chờ nguồn, quản lý DAG, retry 2 lần, SLA 07:00 và backfill theo date range.
+- [1.5 điểm] Phân tích sâu sắc các hạn chế cốt tử của Cron thuần: không nhận biết dữ liệu sẵn sàng, không quản lý được task dependency trong DAG.
+- [1.0 điểm] Nêu rõ các rủi ro vận hành khi chỉ dùng cron (chạy đè, crash do thiếu file, không backfill được).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Bảng yêu cầu kỹ thuật đối với Data Orchestrator:
+| Yêu cầu kỹ thuật | Mô tả chức năng cần thiết |
+|---|---|
+| Dependency &amp; Sensor Waiting | Cần cơ chế Sensor/Event-wait thăm dò cho đến khi cả file bên ngoài và DB snapshot sẵn sàng mới kích hoạt DAG. |
+| Directed Acyclic Graph (DAG) | Quản lý thứ tự thực thi tuần tự có điều kiện: Sensor -&gt; Transform -&gt; Quality Gate -&gt; Publish. |
+| Automated Retry with Backoff | Tự động thử lại tối đa 2 lần cho các lỗi mạng/timeout tạm thời ở từng task độc lập. |
+| SLA &amp; Deadline Alerting | Giám sát mốc SLA 07:00; tự động phát cảnh báo nếu pipeline có nguy cơ không hoàn thành trước giờ cam kết. |
+| Parameterized Backfill Engine | Khả năng chạy lại (backfill) theo dải ngày tùy biến (`start_date` đến `end_date`) một cách độc lập và an toàn. |
+2. Chỉ ra điểm yếu mà cấu hình chỉ có cron thuần túy không thể biểu diễn được:
+   - Cron chỉ là một bộ kích hoạt theo thời gian mù quáng (blind time-trigger). Cron KHÔNG THỂ: (a) Biết nguồn dữ liệu đã sẵn sàng hay chưa (kích hoạt bừa bãi khi file chưa về gây crash); (b) Quản lý trạng thái và phụ thuộc giữa các bước (nếu transform fail, cron không biết cách chặn publish); (c) Tự động retry có giới hạn theo từng task; (d) Thực thi backfill theo tham số lịch sử một cách có kiểm soát.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự khác biệt căn bản giữa một hệ thống điều phối dữ liệu chuyên nghiệp (Data Orchestrator như Apache Airflow, Prefect, Dagster) và công cụ định thời truyền thống (Cron) nằm ở khả năng nhận biết trạng thái phụ thuộc (Stateful Dependency Management). Cron hoàn toàn thiếu nhận thức về dữ liệu (Data-unaware), không thể xử lý việc nguồn bị chậm trễ và không hỗ trợ khôi phục từng phần của DAG khi xảy ra sự cố.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Maxime Beauchemin, 'The Rise of the Data Engineer' &amp; Apache Airflow Architecture: https://airflow.apache.org/ và Dagster - Orchestration Design Principles: https://dagster.io/</t>
         </is>
       </c>
     </row>
@@ -754,10 +768,22 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một transient timeout khác một deterministic schema failure.
-Phân tích theo nguyên lý thiết kế: Một transient timeout khác một deterministic schema failure.</t>
+- [1.5 điểm] Xác định chuẩn xác điểm chạy lại phải bắt đầu từ Task B (nơi sinh ra dữ liệu vi phạm contract), không phải chạy lại từ Task C.
+- [1.5 điểm] Quyết định số lần retry tự động là 0 lần, lập luận thuyết phục dựa trên tính chất lỗi xác định (deterministic failure).
+- [1.0 điểm] Trình bày quy trình xử lý kết thúc: dừng pipeline, thông báo cho kỹ sư chịu trách nhiệm và cách ly output lỗi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn Điểm Chạy Lại (Rerun Point):
+   - Phân tích: Task C thất bại vì 'lỗi schema invalid có tính xác định' (Deterministic Schema Failure), nguyên nhân do output của Task B vi phạm hợp đồng dữ liệu của C. Task A và B tuy chạy thành công về mặt kỹ thuật (exit code 0) nhưng B đã sinh ra dữ liệu sai chuẩn.
+   - Quyết định điểm chạy lại: KHÔNG chạy lại từ Task C một cách mù quáng. Điểm chạy lại bắt buộc phải là TỪ TASK B (hoặc sửa code của Task B rồi chạy lại từ B). Nếu logic của B phụ thuộc vào bản chất transform của A thì giữ nguyên output A, chỉ cần sửa và chạy lại B -&gt; C.
+2. Số lần thử lại (Attempt Count):
+   - Đối với lỗi mang tính xác định (deterministic error): Số lần tự động thử lại (Automatic Retries) = 0 LẦN. Vì dữ liệu đầu vào đã sai ngữ pháp, việc chạy lại 1.000 lần mà không sửa code/rule thì kết quả vẫn thất bại 1.000 lần, chỉ làm lãng phí tài nguyên tính toán.
+3. Cách xử lý khi lỗi kết thúc (End-state Handling):
+   - Lập tức chuyển trạng thái pipeline sang FAILED, phát cảnh báo P2 cho Data Engineer phụ trách Task B;
+   - Toàn bộ output sai định dạng của Task B bị đưa vào Quarantine, ngăn chặn việc nạp tiếp vào các downstream tasks tiếp theo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kỹ nghệ xử lý lỗi đường ống dữ liệu, nguyên tắc sống còn là 'Phân biệt giữa lỗi tạm thời (Transient Failure) và lỗi đơn định (Deterministic Failure)'. Lỗi tạm thời (như rớt mạng, timeout) thì cần retry có backoff. Ngược lại, lỗi vi phạm schema là lỗi logic có tính tất định: nếu không có sự can thiệp sửa đổi mã nguồn hoặc dữ liệu đầu vào, việc retry chỉ tạo ra lãng phí và nguy cơ làm nghẽn hàng đợi. Phải dừng retry tự động và yêu cầu sửa lỗi tại trạm sinh ra lỗi (Task B).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Handling Overload &amp; Transient vs Permanent Errors: https://sre.google/sre-book/addressing-cascading-failures/ và Temporal.io Workflow Failure Handling Guides</t>
         </is>
       </c>
     </row>
@@ -837,10 +863,23 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách write completion khỏi serving activation.
-Phân tích theo nguyên lý thiết kế: Tách write completion khỏi serving activation.</t>
+- [1.5 điểm] Chỉ rõ nguyên nhân gây lỗi: nạp trực tiếp vào live collection gây ra đọc dữ liệu dở dang (partial read).
+- [1.5 điểm] Thiết kế giải pháp Blue/Green Indexing hoàn chỉnh: nạp trọn vẹn 1M vectors vào staging collection và chuyển đổi bằng Atomic Alias Swap.
+- [1.0 điểm] Xây dựng phương án rollback tức thì bằng cách trỏ ngược lại alias về collection ban đầu mà không mất mát dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế lại Ranh giới Publish Nguyên tử (Atomic Publish Boundary):
+   - Sai lầm hiện tại: Nạp trực tiếp dữ liệu đang rebuild (600k/1M) vào Live Collection đang phục vụ truy vấn, khiến Agent đọc phải trạng thái 'dữ liệu dở dang' (partial / dirty read anomaly).
+   - Thiết kế chuẩn (Blue/Green Collection &amp; Alias Pointer Swap):
+     + Serving Layer luôn truy vấn thông qua một alias logic cố định: `vector_index_active`.
+     + Quá trình Rebuild 1M vectors được thực hiện hoàn toàn độc lập trên một Collection ẩn / staging mới: `vector_index_v2_staging` (không có user traffic).
+     + Toàn bộ 1.000.000 vectors được nạp và build chỉ mục (HNSW / IVF-PQ) hoàn tất trên collection mới, sau đó chạy bộ kiểm thử chất lượng (Sanity &amp; Quality Verification Check).
+     + Khi và chỉ khi 1M vectors đạt 100% chuẩn, thực hiện thao tác chuyển đổi con trỏ nguyên tử (Atomic Alias Swap): Trỏ alias `vector_index_active` từ `v1` sang `v2` trong thời gian mili-giây (Zero Downtime, Zero Partial Read).
+2. Thiết kế Cơ chế Rollback tức thì:
+   - Nếu phát hiện lỗi sau khi chuyển đổi, chỉ cần một thao tác lệnh đơn lẻ (Atomic Pointer Switch) trỏ alias `vector_index_active` quay trở lại Collection cũ `v1` (vẫn được lưu giữ nguyên vẹn trong 48 giờ).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc cập nhật các tập dữ liệu lớn và chỉ mục tìm kiếm (Vector Indices) bắt buộc phải tuân thủ nguyên lý 'Phân tách giữa Quá trình Xây dựng và Quá trình Xuất bản' (Separation of Build Completion and Serving Activation). Sử dụng mẫu hình Blue/Green với Alias trỏ nguyên tử giúp loại bỏ hoàn toàn hiện tượng người dùng nhìn thấy dữ liệu đang nạp dở dang, đồng thời cung cấp phương án phục hồi thảm họa (instant rollback) với thời gian phục hồi gần như bằng không.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Qdrant / Milvus Vector Database Documentation - Collection Aliases &amp; Zero-Downtime Reindexing: https://qdrant.tech/documentation/concepts/collections/#collection-aliases và Martin Kleppmann, Designing Data-Intensive Applications</t>
         </is>
       </c>
     </row>
@@ -871,10 +910,21 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định range, identity và điểm result trở thành production.
-Phân tích theo nguyên lý thiết kế: Xác định range, identity và điểm result trở thành production.</t>
+- [1.5 điểm] Giới hạn chính xác phạm vi backfill (đúng 3 phân vùng 2026-04-01..03) và cách ly định danh/tài nguyên với pipeline production trực tiếp.
+- [1.5 điểm] Thiết kế cơ chế ghi đè phân vùng nguyên tử (Atomic Partition Overwrite / Swap) trên Delta Lake / Iceberg để tránh xung đột ghi.
+- [1.0 điểm] Bổ sung quality gate kiểm định trên staging trước khi tích hợp vào serving layer.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Bounded Backfill an toàn không phá vỡ Production:
+   - Phạm vi giới hạn rõ ràng (Bounded Scope): Thiết lập tham số cứng `start_date='2026-04-01'` và `end_date='2026-04-03'` (chính xác 3 ngày thiếu, không quét ngoài phạm vi).
+   - Tách biệt định danh thực thi (Execution Identity Isolation): Tác vụ backfill phải chạy dưới một `run_id` và worker pool riêng biệt (ví dụ `backfill_20260401_03_run`), được giới hạn tài nguyên (CPU/Memory/IOPS limit) để không tranh chấp hoặc làm cạn kiệt tài nguyên của pipeline trực tiếp đang phục vụ thời gian thực.
+2. Điểm kết quả trở thành Production (Promotion to Production Boundary):
+   - Dữ liệu sau khi xử lý được ghi tạm vào vùng đệm staging phân vùng: `staging/partition_date=2026-04-01/`...
+   - Chạy Data Quality Gate độc lập trên 3 phân vùng này để xác nhận tính toàn vẹn.
+   - Ghi vào Production bằng thao tác ghi đè phân vùng nguyên tử (Atomic Partition Overwrite): Áp dụng lệnh `INSERT OVERWRITE TABLE ... PARTITION (dt IN ('2026-04-01', '2026-04-02', '2026-04-03'))` trên Apache Iceberg / Delta Lake. Thao tác này chỉ cập nhật metadata catalog của đúng 3 phân vùng thiếu mà không làm khóa hoặc ảnh hưởng đến các phân vùng đang nạp trực tiếp của ngày hôm nay.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thực hiện bù dữ liệu lịch sử (Data Backfilling) trong khi luồng trực tiếp vẫn đang chạy đồng thời tiềm ẩn rủi ro xung đột ghi (Write Conflict) và cạn kiệt tài nguyên hệ thống. Thiết kế an toàn đòi hỏi: (1) Cách ly tài nguyên và định danh thực thi; (2) Giới hạn phạm vi phân vùng nghiêm ngặt; (3) Áp dụng cơ chế cập nhật phân vùng nguyên tử (Atomic Partition Replacement) của các định dạng bảng hiện đại (Delta/Iceberg) để loại bỏ race condition.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Apache Iceberg Documentation - ACID Partition Evolution &amp; Overwrites: https://iceberg.apache.org/ và Databricks Guide on Safe Historical Backfilling</t>
         </is>
       </c>
     </row>
@@ -1044,10 +1094,22 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một check chỉ được giữ nếu kết quả có thể đổi hypothesis/decision.
-Phân tích theo nguyên lý thiết kế: Một check chỉ được giữ nếu kết quả có thể đổi hypothesis/decision.</t>
+- [1.5 điểm] Phân bổ hợp lý thời gian trong khung 20 phút, ưu tiên kiểm tra nhanh các chỉ số sẵn có trong log (last_success, counts, schema_hash).
+- [1.5 điểm] Áp dụng đúng Stop Rule loại bỏ việc chạy truy vấn lineage 10 phút vì quá tốn thời gian và không thay đổi quyết định mitigation.
+- [1.0 điểm] Đưa ra phương án mitigation bàn giao rõ ràng (rollback serving alias về snapshot ổn định trước khi hết giờ).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lập kế hoạch Timebox 20 phút với Stop Rule cụ thể:
+   - Phút 0 - 5 (Phân tích Logs nhanh - High-Leverage Check): Kiểm tra ngay các trường có sẵn trong log: `last_success_timestamp`, `processed_row_counts` và `schema_hash`. Mục tiêu: Xác định xem pipeline có chạy hay bị kẹt, số lượng bản ghi có bị rớt về 0 không, và schema có bị đổi không.
+   - Phút 5: ĐÁNH GIÁ STOP RULE 1 -&gt; Nếu logs cho thấy lần chạy gần nhất fail hoặc `processed_row_counts == 0`, STOP ngay lập tức, không đào sâu thêm, chuyển sang kích hoạt Mitigation.
+   - Áp dụng Stop Rule với Lineage Query (10 phút): Truy vấn lineage mất tới 10 phút (chiếm 50% tổng thời gian). STOP RULE: LOẠI BỎ / HOÃN TRUY VẤN LINEAGE trong khung 20 phút này! Lý do: Trong tình huống khẩn cấp, nếu kết quả của lineage query không làm thay đổi quyết định giảm thiểu tức thì, thì việc đợi 10 phút là lãng phí thời gian ứng cứu.
+   - Phút 6 - 15 (Xác nhận Artifact Serving): Kiểm tra xem Index Alias đang trỏ vào snapshot nào.
+2. Bàn giao Mitigation (Giảm thiểu sự cố lúc phút 15 - 20):
+   - Thực hiện rollback serving alias về snapshot tốt đã biết trước đó (Known-Good Snapshot);
+   - Bàn giao cho nhóm Data Platform tiếp tục chạy lineage query ngoại tuyến để phân tích nguyên nhân gốc sau khi hệ thống đã an toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong xử lý sự cố khẩn cấp (Incident Triage), thời gian là tài nguyên quý giá nhất. Quy tắc vàng của SRE là 'Ưu tiên Giảm thiểu sự cố trước khi Tìm nguyên nhân gốc' (Mitigate first, Root-cause later). Một bước kiểm tra chỉ được phép thực hiện nếu nó mang lại thông tin trực tiếp phục vụ quyết định giảm thiểu rủi ro. Các truy vấn tốn nhiều thời gian (như lineage query 10 phút) phải bị cắt bỏ nếu hệ thống đã có đủ thông tin từ log để thực hiện hành động khắc phục tạm thời.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Emergency Response &amp; Managing Incidents: https://sre.google/sre-book/incident-management/ và PagerDuty Incident Response Documentation</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1140,23 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chọn hành động có thể đảo ngược trong khi root cause chưa chắc.
-Phân tích theo nguyên lý thiết kế: Chọn hành động có thể đảo ngược trong khi root cause chưa chắc.</t>
+- [1.5 điểm] Lựa chọn chính xác mitigation có thể đảo ngược: chuyển serving alias về v2 (known-good), giữ v3 offline để debug.
+- [1.5 điểm] Xây dựng thông điệp công bố minh bạch và chuẩn mực cho người dùng về việc tạm thời dùng dữ liệu lùi 1 ngày.
+- [1.0 điểm] Thiết lập đầy đủ tiêu chí kết thúc sự cố: fix root cause, tạo v4 đạt chuẩn, switch alias an toàn và quan sát ổn định.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn Mitigation có thể đảo ngược (Reversible Mitigation):
+   - Thực hiện chuyển hướng Serving Alias (Atomic Alias Re-point) từ `index_v3` quay trở lại `index_v2`. Dù v2 cũ 1 ngày (stale 1 day), nhưng v2 là 'Known-Good' (dữ liệu chính sách đã được kiểm chứng chuẩn xác), tốt hơn vô cùng việc tiếp tục phục vụ v3 chứa chính sách sai lệch nghiêm trọng cho người dùng.
+   - Tính chất đảo ngược: Giữ nguyên v3 ở trạng thái offline/quarantine; khi nào root cause được sửa và xác nhận, chỉ cần một lệnh switch alias là có thể chuyển lại mà không làm mất dữ liệu.
+2. Cách công bố (Incident Communication):
+   - Thông báo minh bạch cho các bên liên quan và người dùng RAG Agent: 'Hệ thống tri thức hiện đang tạm thời sử dụng bản snapshot chính sách ngày hôm qua để khắc phục sự cố hiển thị. Các cập nhật trong 24 giờ qua đang được rà soát lại và sẽ có thông báo khi hoàn tất'.
+3. Tiêu chí kết thúc sự cố (Exit Criteria):
+   - Nguyên nhân gốc của việc sinh ra policy sai trong v3 được xác định, sửa chữa bằng code/rule và vượt qua bộ kiểm thử hồi quy;
+   - Tạo thành công `index_v4` từ dữ liệu đã sửa, kiểm định đạt 100% độ chính xác;
+   - Hoàn tất switch alias sang v4 và theo dõi trong 2 giờ không có lỗi phát sinh.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong quản lý sự cố dữ liệu khi chưa làm rõ nguyên nhân gốc (unclosed root cause), nguyên tắc an toàn cao nhất là 'Lùi về trạng thái ổn định đã biết' (Rollback to Known-Good State). Việc chấp nhận độ trễ thời gian (stale 1 ngày) để đổi lấy tính chính xác tuyệt đối là sự đánh đổi bắt buộc trong các miền nghiệp vụ quan trọng (pháp lý, chính sách). Mọi giải pháp ứng cứu phải có tính khả nghịch (reversible) và đi kèm tiêu chí nghiệm thu nghiêm ngặt trước khi đóng sự cố.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+PagerDuty Incident Response Guides - Rollback and Mitigation Strategies: https://response.pagerduty.com/ và Google SRE Book - Postmortem Culture</t>
         </is>
       </c>
     </row>
@@ -1163,10 +1238,21 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Control mới phải fail trên chính corruption case này.
-Phân tích theo nguyên lý thiết kế: Control mới phải fail trên chính corruption case này.</t>
+- [1.5 điểm] Lập bản ghi nguyên nhân (causal record) chỉ rõ cơ chế lỗi do parser nuốt lỗi im lặng (lenient fallback) khi schema rename và chỉ ra sự nguy hiểm của việc chỉ sửa tay.
+- [1.5 điểm] Thiết kế cơ chế kiểm soát phòng ngừa chặt chẽ (Strict Schema Enforcement / Great Expectations contract).
+- [1.0 điểm] Chứng minh tính kiểm thử được của control: bắt buộc phải fail trên chính ca biến dạng dữ liệu lịch sử trong bài kiểm thử tự động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Viết Causal Record (Bản ghi nguyên nhân sự cố):
+   - Sự kiện sự cố: Parser âm thầm bỏ qua một cột quan trọng sau khi schema phía nguồn đổi tên (Schema Rename Silent Drop Incident).
+   - Cơ chế phát sinh lỗi: Parser sử dụng cấu hình nới lỏng (lenient / permissive mode) hoặc truy cập thuộc tính bằng cú pháp fallback `dict.get('old_col_name', None)`. Khi cột bị rename, parser nhận `None` mà không báo lỗi, tiếp tục ghi dữ liệu thiếu vào canonical store. Đội ngũ sau đó đã can thiệp sửa tay thủ công các dòng lỗi.
+   - Điểm yếu quy trình: Sửa tay bằng cơm không tạo ra rào cản ngăn chặn tái diễn; thiếu kiểm thử hồi quy tự động.
+2. Thiết kế Prevention Control có thể test được (Testable Prevention Control):
+   - Xây dựng Data Contract Test bắt buộc trong CI/CD và Pipeline Runtime: Triển khai kiểm thử `Strict Schema Validation` bằng Pydantic hoặc Great Expectations (`expect_table_columns_to_match_ordered_set`). Cấm hoàn toàn việc bỏ qua cột bắt buộc.
+   - Kiểm chứng tính hiệu quả của Control mới: Tạo một Unit/Integration Test đưa chính payload bị lỗi (với tên cột đã rename nhưng chưa cập nhật parser) qua control mới. TIÊU CHÍ BẮT BUỘC: Control mới PHẢI FAIL (báo lỗi SchemaValidationError) ngay lập tức trên chính ca dữ liệu biến dạng này, chứng minh hệ thống không còn bị rơi vào tình trạng âm thầm bỏ sót cột nữa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một chu trình ngăn ngừa sự cố dữ liệu (Data Incident Prevention Loop) thực sự chỉ hoàn tất khi ta xây dựng được một rào kiểm soát có thể kiểm thử (Testable Control) có khả năng 'bắt được chính kẻ thù cũ'. Việc sửa tay chỉ là giải pháp tình thế (band-aid). Phép kiểm tra tính hiệu quả của cơ chế phòng vệ là: khi đưa trường hợp lỗi lịch sử vào kiểm thử hồi quy, hệ thống bắt buộc phải phát hiện và từ chối xử lý thay vì im lặng cho qua.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Incident Prevention and Postmortem Action Items: https://sre.google/sre-book/postmortem-culture/ và Great Expectations - Schema Validation Rules</t>
         </is>
       </c>
     </row>
